--- a/data/kz/niches/niche_formats_SUGARING.xlsx
+++ b/data/kz/niches/niche_formats_SUGARING.xlsx
@@ -502,6 +502,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -595,7 +596,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -641,12 +642,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_RENT</t>
+          <t>SUGARING_SOLO</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
@@ -692,12 +693,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -768,6 +769,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,12 +825,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -861,12 +863,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -899,12 +901,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -937,12 +939,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1007,6 +1009,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1057,12 +1060,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1090,12 +1093,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1158,6 +1161,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1257,6 +1261,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1571,6 +1576,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1715,6 +1721,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1800,7 +1807,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1854,12 +1861,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_RENT</t>
+          <t>SUGARING_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1913,12 +1920,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2018,6 +2025,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2143,7 +2151,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2213,12 +2221,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_RENT</t>
+          <t>SUGARING_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2288,12 +2296,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2399,6 +2407,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2474,7 +2483,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2516,12 +2525,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_RENT</t>
+          <t>SUGARING_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2559,12 +2568,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2638,6 +2647,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2713,7 +2723,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2753,12 +2763,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_RENT</t>
+          <t>SUGARING_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2798,12 +2808,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2876,6 +2886,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2936,7 +2947,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2973,12 +2984,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_RENT</t>
+          <t>SUGARING_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3015,12 +3026,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3093,6 +3104,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3168,7 +3180,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3224,12 +3236,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_RENT</t>
+          <t>SUGARING_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3285,12 +3297,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3377,6 +3389,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3427,7 +3440,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -3461,7 +3474,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -3495,7 +3508,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -3529,7 +3542,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3585,6 +3598,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3610,12 +3624,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3632,12 +3646,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SUGARING_OWN</t>
+          <t>SUGARING_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
